--- a/InputData/land/RPEpUACE/Rebound Pol Emis per Unit Avoided CO2 Emis.xlsx
+++ b/InputData/land/RPEpUACE/Rebound Pol Emis per Unit Avoided CO2 Emis.xlsx
@@ -1,29 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\Dropbox\EPS\Input Data for India 2.0\land\RPEpUACE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\land\RPEpUACE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1013EB59-E2B6-4BC2-B2F8-7F5043DA2D8C}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0C39C8-7140-4E9A-800C-6D86145E4794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Calculations" sheetId="4" r:id="rId3"/>
-    <sheet name="RPEpUACE" sheetId="3" r:id="rId4"/>
+    <sheet name="RPEpUACE" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="61">
   <si>
     <t>RPEpUACE Rebound Pollutant Emissions per Unit Avoided CO2 Emissions</t>
   </si>
@@ -66,109 +69,154 @@
     <t>N2O</t>
   </si>
   <si>
+    <t>Unit: kt</t>
+  </si>
+  <si>
+    <t>VOC</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>NOx</t>
+  </si>
+  <si>
+    <t>PM10</t>
+  </si>
+  <si>
+    <t>PM25</t>
+  </si>
+  <si>
+    <t>SOx</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>OC</t>
+  </si>
+  <si>
+    <t>F gases</t>
+  </si>
+  <si>
+    <t>Rebound Emis Factor (dimensionless)</t>
+  </si>
+  <si>
+    <t>US EPA</t>
+  </si>
+  <si>
+    <t>Table 6-3</t>
+  </si>
+  <si>
+    <t>Table 6-3:  Emissions and Removals from Land Use, Land-Use Change, and Forestry by Gas (kt)</t>
+  </si>
+  <si>
+    <t>Gas/Land-Use Category</t>
+  </si>
+  <si>
+    <t>Carbon Stock Change (CO2)a</t>
+  </si>
+  <si>
+    <t>Forest Land Remaining Forest Land</t>
+  </si>
+  <si>
+    <t>Land Converted to Forest Land</t>
+  </si>
+  <si>
+    <t>Cropland Remaining Cropland</t>
+  </si>
+  <si>
+    <t>Land Converted to Cropland</t>
+  </si>
+  <si>
+    <t>Grassland Remaining Grassland</t>
+  </si>
+  <si>
+    <t>Land Converted to Grassland</t>
+  </si>
+  <si>
+    <t>Wetlands Remaining Wetlands</t>
+  </si>
+  <si>
+    <t>Land Converted to Wetlands</t>
+  </si>
+  <si>
+    <t>Settlements Remaining Settlements</t>
+  </si>
+  <si>
+    <t>Land Converted to Settlements</t>
+  </si>
+  <si>
+    <t>Forest Land Remaining Forest Land: Forest Firesb</t>
+  </si>
+  <si>
+    <t>Forest Land Remaining Forest Land: Drained Organic Soilsd</t>
+  </si>
+  <si>
+    <t>Grassland Remaining Grassland: Grassland Firesc</t>
+  </si>
+  <si>
+    <t>Wetlands Remaining Wetlands: Flooded Land Remaining Flooded Land</t>
+  </si>
+  <si>
+    <t>Wetlands Remaining Wetlands: Coastal Wetlands Remaining Coastal Wetlands</t>
+  </si>
+  <si>
+    <t>Wetlands Remaining Wetlands: Peatlands Remaining Peatlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ </t>
+  </si>
+  <si>
+    <t>Land Converted to Wetlands: Land Converted to Flooded Lands</t>
+  </si>
+  <si>
+    <t>Land Converted to Wetlands: Land Converted to Coastal Wetlands</t>
+  </si>
+  <si>
+    <t>Forest Land Remaining Forest Land: Forest Soilsf</t>
+  </si>
+  <si>
+    <t>Settlements Remaining Settlements: Settlement Soilse</t>
+  </si>
+  <si>
+    <t>+ Absolute value does not exceed 0.5 kt.</t>
+  </si>
+  <si>
+    <t>a LULUCF Carbon Stock Change is the net C stock change from the following categories: Forest Land Remaining Forest Land, Land Converted to Forest Land, Cropland Remaining Cropland, Land Converted to Cropland, Grassland Remaining Grassland, Land Converted to Grassland, Wetlands Remaining Wetlands, Land Converted to Wetlands, Settlements Remaining Settlements, and Land Converted to Settlements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b Estimates include CH4 and N2O emissions from fires on both Forest Land Remaining Forest Land and Land Converted to Forest Land. </t>
+  </si>
+  <si>
+    <t>c Estimates include CH4 and N2O emissions from drained organic soils on both Forest Land Remaining Forest Land and Land Converted to Forest Land.</t>
+  </si>
+  <si>
+    <t>d Estimates include CH4 and N2O emissions from fires on both Grassland Remaining Grassland and Land Converted to Grassland.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e Estimates include N2O emissions from N fertilizer additions on both Forest Land Remaining Forest Land and Land Converted to Forest Land. </t>
+  </si>
+  <si>
+    <t>f Estimates include N2O emissions from N fertilizer additions on both Settlements Remaining Settlements and Land Converted to Settlements.</t>
+  </si>
+  <si>
+    <t>Notes: Totals may not sum due to independent rounding. Parentheses indicate net sequestration.</t>
+  </si>
+  <si>
+    <t>https://www.epa.gov/ghgemissions/inventory-us-greenhouse-gas-emissions-and-sinks-1990-2020</t>
+  </si>
+  <si>
+    <t>Table 6-3:</t>
+  </si>
+  <si>
+    <t>Inventory of US Greenhouse Gas Emissions Emissions and Sinks: 1990-2020</t>
+  </si>
+  <si>
     <t>CH4/CO2 Ratio</t>
   </si>
   <si>
     <t>N2O/CO2 Ratio</t>
-  </si>
-  <si>
-    <t>VOC</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
-    <t>NOx</t>
-  </si>
-  <si>
-    <t>PM10</t>
-  </si>
-  <si>
-    <t>PM25</t>
-  </si>
-  <si>
-    <t>SOx</t>
-  </si>
-  <si>
-    <t>BC</t>
-  </si>
-  <si>
-    <t>OC</t>
-  </si>
-  <si>
-    <t>F gases</t>
-  </si>
-  <si>
-    <t>Rebound Emis Factor</t>
-  </si>
-  <si>
-    <t>LULUCF</t>
-  </si>
-  <si>
-    <t>CO2 Emissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CO2 Removals </t>
-  </si>
-  <si>
-    <t>N20</t>
-  </si>
-  <si>
-    <t>CO2e</t>
-  </si>
-  <si>
-    <t>Net CO2 Emissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rebound Emissions </t>
-  </si>
-  <si>
-    <t>2010 (Gg)</t>
-  </si>
-  <si>
-    <t>Table 2.2: Greenhouse gas emissions, by sectors, for India in 2010</t>
-  </si>
-  <si>
-    <t>Ministry of Environment, Forest and Climate Change</t>
-  </si>
-  <si>
-    <t>First Biennial Update Report to the UNFCCC</t>
-  </si>
-  <si>
-    <t>unfccc.int/resource/docs/natc/indbur1.pdf</t>
-  </si>
-  <si>
-    <t>Table 2.2: GHG Emissions by sector (Gg) (First Biennial Report - 2010)</t>
-  </si>
-  <si>
-    <t>Table 2.2: GHG Emissions by sector (Gg) (Second Biennial Report - 2014)</t>
-  </si>
-  <si>
-    <t>2014 (Gg)</t>
-  </si>
-  <si>
-    <t>GHG Emissions (2010)</t>
-  </si>
-  <si>
-    <t>GHG Emissions (2014)</t>
-  </si>
-  <si>
-    <t>Second Biennial Update Report to the UNFCCC</t>
-  </si>
-  <si>
-    <t>https://unfccc.int/sites/default/files/resource/INDIA%20SECOND%20BUR%20High%20Res.pdf</t>
-  </si>
-  <si>
-    <t>Table 2.2: Greenhouse gas emissions, by sectors, for India in 2014</t>
-  </si>
-  <si>
-    <t>For India, historical CH4/N2O emissions are available for the LULUCF sector only</t>
-  </si>
-  <si>
-    <t>for 2012 &amp; 2014, in the Biennial reports. We use the ratios from the same to</t>
-  </si>
-  <si>
-    <t>estimate the average value to be applied to future years.</t>
   </si>
 </sst>
 </file>
@@ -200,18 +248,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -227,7 +269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -235,10 +277,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -578,110 +617,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="11" max="11" width="57.85546875" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="K3" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -692,251 +691,720 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>2016</v>
+      </c>
+      <c r="C4">
+        <v>2017</v>
+      </c>
+      <c r="D4">
+        <v>2018</v>
+      </c>
+      <c r="E4">
+        <v>2019</v>
+      </c>
+      <c r="F4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5">
+        <v>-862045</v>
+      </c>
+      <c r="C5" s="5">
+        <v>-826667</v>
+      </c>
+      <c r="D5" s="5">
+        <v>-809026</v>
+      </c>
+      <c r="E5" s="5">
+        <v>-760820</v>
+      </c>
+      <c r="F5" s="5">
+        <v>-812176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="5">
+        <v>-725571</v>
+      </c>
+      <c r="C6" s="5">
+        <v>-688301</v>
+      </c>
+      <c r="D6" s="5">
+        <v>-677101</v>
+      </c>
+      <c r="E6" s="5">
+        <v>-634824</v>
+      </c>
+      <c r="F6" s="5">
+        <v>-668057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="5">
+        <v>-99454</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-99523</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-99518</v>
+      </c>
+      <c r="E7" s="5">
+        <v>-99520</v>
+      </c>
+      <c r="F7" s="5">
+        <v>-99521</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5">
+        <v>-22731</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-22293</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-16597</v>
+      </c>
+      <c r="E8" s="5">
+        <v>-14544</v>
+      </c>
+      <c r="F8" s="5">
+        <v>-23335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5">
+        <v>54107</v>
+      </c>
+      <c r="C9" s="5">
+        <v>54273</v>
+      </c>
+      <c r="D9" s="5">
+        <v>53975</v>
+      </c>
+      <c r="E9" s="5">
+        <v>53935</v>
+      </c>
+      <c r="F9" s="5">
+        <v>54380</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="5">
+        <v>7958</v>
+      </c>
+      <c r="C10" s="5">
+        <v>9308</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9670</v>
+      </c>
+      <c r="E10" s="5">
+        <v>12425</v>
+      </c>
+      <c r="F10" s="5">
+        <v>4497</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="5">
+        <v>-22553</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-22693</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-22397</v>
+      </c>
+      <c r="E11" s="5">
+        <v>-21485</v>
+      </c>
+      <c r="F11" s="5">
+        <v>-24101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5">
+        <v>-8046</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-7954</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-7994</v>
+      </c>
+      <c r="E12" s="5">
+        <v>-8034</v>
+      </c>
+      <c r="F12" s="5">
+        <v>-8084</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13">
+        <v>254</v>
+      </c>
+      <c r="C13">
+        <v>258</v>
+      </c>
+      <c r="D13">
+        <v>265</v>
+      </c>
+      <c r="E13">
+        <v>271</v>
+      </c>
+      <c r="F13">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="B14" s="5">
+        <v>-123794</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-127679</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-127299</v>
+      </c>
+      <c r="E14" s="5">
+        <v>-126977</v>
+      </c>
+      <c r="F14" s="5">
+        <v>-126128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5">
+        <v>77784</v>
+      </c>
+      <c r="C15" s="5">
+        <v>77938</v>
+      </c>
+      <c r="D15" s="5">
+        <v>77970</v>
+      </c>
+      <c r="E15" s="5">
+        <v>77932</v>
+      </c>
+      <c r="F15" s="5">
+        <v>77895</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1131</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1359</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1226</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1022</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17">
+        <v>154</v>
+      </c>
+      <c r="C17">
+        <v>381</v>
+      </c>
+      <c r="D17">
+        <v>249</v>
+      </c>
+      <c r="E17">
+        <v>45</v>
+      </c>
+      <c r="F17">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19">
+        <v>11</v>
+      </c>
+      <c r="C19">
+        <v>12</v>
+      </c>
+      <c r="D19">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20">
+        <v>796.7</v>
+      </c>
+      <c r="C20">
+        <v>796.8</v>
+      </c>
+      <c r="D20">
+        <v>796.9</v>
+      </c>
+      <c r="E20">
+        <v>796.9</v>
+      </c>
+      <c r="F20">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21">
+        <v>153</v>
+      </c>
+      <c r="C21">
+        <v>153</v>
+      </c>
+      <c r="D21">
+        <v>153</v>
+      </c>
+      <c r="E21">
+        <v>153</v>
+      </c>
+      <c r="F21">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>7</v>
+      </c>
+      <c r="E23">
+        <v>7</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>8</v>
+      </c>
+      <c r="D24">
+        <v>7</v>
+      </c>
+      <c r="E24">
+        <v>7</v>
+      </c>
+      <c r="F24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C25">
+        <v>39</v>
+      </c>
+      <c r="D25">
+        <v>31</v>
+      </c>
+      <c r="E25">
+        <v>16</v>
+      </c>
+      <c r="F25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26">
+        <v>13</v>
+      </c>
+      <c r="C26">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="5">
-        <v>58261.7</v>
-      </c>
-      <c r="C3" s="5">
-        <v>314586.77</v>
-      </c>
-      <c r="D3">
-        <v>153.02000000000001</v>
-      </c>
-      <c r="E3">
-        <v>1.87</v>
-      </c>
-      <c r="F3" s="5">
-        <v>-252531.78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="5">
-        <f>B3-C3</f>
-        <v>-256325.07</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="8">
-        <v>17216.04</v>
-      </c>
-      <c r="C10" s="8">
-        <v>319860.23</v>
-      </c>
-      <c r="D10">
-        <v>48.19</v>
-      </c>
-      <c r="E10">
-        <v>1.42</v>
-      </c>
-      <c r="F10" s="5">
-        <v>-301192.69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="8">
-        <f>B10-C10</f>
-        <v>-302644.19</v>
+      <c r="D26">
+        <v>19</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32">
+        <v>8</v>
+      </c>
+      <c r="D32">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="3">
+        <f>B16/B5</f>
+        <v>-1.3119964735019633E-3</v>
+      </c>
+      <c r="C43" s="3">
+        <f t="shared" ref="C43:F43" si="0">C16/C5</f>
+        <v>-1.6439509500197783E-3</v>
+      </c>
+      <c r="D43" s="3">
+        <f t="shared" si="0"/>
+        <v>-1.5154024716140149E-3</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="0"/>
+        <v>-1.3432875055860781E-3</v>
+      </c>
+      <c r="F43" s="3">
+        <f t="shared" si="0"/>
+        <v>-1.8739780540178485E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="3">
+        <f>B25/B5</f>
+        <v>-2.7840773973516463E-5</v>
+      </c>
+      <c r="C44" s="3">
+        <f t="shared" ref="C44:F44" si="1">C25/C5</f>
+        <v>-4.7177400331693413E-5</v>
+      </c>
+      <c r="D44" s="3">
+        <f t="shared" si="1"/>
+        <v>-3.8317680766749151E-5</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" si="1"/>
+        <v>-2.1029941379038406E-5</v>
+      </c>
+      <c r="F44" s="3">
+        <f t="shared" si="1"/>
+        <v>-6.2794271192450897E-5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5">
-        <f>Data!B6</f>
-        <v>-256325.07</v>
-      </c>
-      <c r="C4" s="8">
-        <f>Data!B13</f>
-        <v>-302644.19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
-        <f>Data!D3</f>
-        <v>153.02000000000001</v>
-      </c>
-      <c r="C5">
-        <f>Data!D10</f>
-        <v>48.19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6">
-        <f>Data!E3</f>
-        <v>1.87</v>
-      </c>
-      <c r="C6">
-        <f>Data!E10</f>
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3">
-        <f t="shared" ref="B8:C8" si="0">B5/B4</f>
-        <v>-5.9697633165573698E-4</v>
-      </c>
-      <c r="C8" s="3">
-        <f t="shared" si="0"/>
-        <v>-1.5922988642207207E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="3">
-        <f t="shared" ref="B9:C9" si="1">B6/B4</f>
-        <v>-7.2954237367417868E-6</v>
-      </c>
-      <c r="C9" s="3">
-        <f t="shared" si="1"/>
-        <v>-4.6919783921839041E-6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -944,91 +1412,91 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="3">
-        <f>-AVERAGE(Calculations!B8, Calculations!C8)</f>
-        <v>3.781031090389045E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <f>-AVERAGE(Data!B43:F43)</f>
+        <v>1.5377230909479366E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <f>-AVERAGE(Calculations!B9,Calculations!C9)</f>
-        <v>5.9937010644628454E-6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <f>-AVERAGE(Data!B44:F44)</f>
+        <v>3.9432013528689668E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>0</v>
